--- a/Hospital_Qswift_Login_E2E_Test_Report.xlsx
+++ b/Hospital_Qswift_Login_E2E_Test_Report.xlsx
@@ -62,7 +62,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>28/10/2026, 8:38:03 pm</t>
+    <t>28/10/2026, 11:42:36 pm</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>

--- a/Hospital_Qswift_Login_E2E_Test_Report.xlsx
+++ b/Hospital_Qswift_Login_E2E_Test_Report.xlsx
@@ -62,7 +62,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>28/10/2026, 11:42:36 pm</t>
+    <t>29/10/2026, 12:02:54 am</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>

--- a/Hospital_Qswift_Login_E2E_Test_Report.xlsx
+++ b/Hospital_Qswift_Login_E2E_Test_Report.xlsx
@@ -62,7 +62,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>29/10/2026, 12:02:54 am</t>
+    <t>29/10/2026, 12:06:32 am</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>
